--- a/artfynd/A 8551-2026 artfynd.xlsx
+++ b/artfynd/A 8551-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015502</v>
       </c>
       <c r="B2" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>132015501</v>
       </c>
       <c r="B3" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>132015515</v>
       </c>
       <c r="B4" t="n">
-        <v>80408</v>
+        <v>80409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>132015509</v>
       </c>
       <c r="B5" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>132015446</v>
       </c>
       <c r="B6" t="n">
-        <v>83248</v>
+        <v>83249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132015469</v>
       </c>
       <c r="B7" t="n">
-        <v>80402</v>
+        <v>80403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>132015510</v>
       </c>
       <c r="B8" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>132015512</v>
       </c>
       <c r="B9" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>132015496</v>
       </c>
       <c r="B10" t="n">
-        <v>80373</v>
+        <v>80374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>132015463</v>
       </c>
       <c r="B11" t="n">
-        <v>58065</v>
+        <v>58066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 8551-2026 artfynd.xlsx
+++ b/artfynd/A 8551-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015502</v>
       </c>
       <c r="B2" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>132015501</v>
       </c>
       <c r="B3" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>132015515</v>
       </c>
       <c r="B4" t="n">
-        <v>80409</v>
+        <v>80414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>132015509</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>132015446</v>
       </c>
       <c r="B6" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132015469</v>
       </c>
       <c r="B7" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>132015510</v>
       </c>
       <c r="B8" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>132015512</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>132015496</v>
       </c>
       <c r="B10" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>132015463</v>
       </c>
       <c r="B11" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 8551-2026 artfynd.xlsx
+++ b/artfynd/A 8551-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015502</v>
       </c>
       <c r="B2" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>132015501</v>
       </c>
       <c r="B3" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>132015515</v>
       </c>
       <c r="B4" t="n">
-        <v>80414</v>
+        <v>80416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>132015509</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>132015446</v>
       </c>
       <c r="B6" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>132015469</v>
       </c>
       <c r="B7" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>132015510</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>132015512</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>132015496</v>
       </c>
       <c r="B10" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>132015463</v>
       </c>
       <c r="B11" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
